--- a/kursovoy-viv/excel/Расчёт расходов воды (СП 30).xlsx
+++ b/kursovoy-viv/excel/Расчёт расходов воды (СП 30).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kursovoy\.claude\worktrees\kursovoy-viv-variant-3-388c78\kursovoy-viv\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8551463-A95A-4042-8878-0B2B98FA92AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F18B98-3940-461A-B759-FAF221131199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="134">
   <si>
     <t>Расчёт расходов воды по СП 30.13330.2020 (п. 5, табл. А.2, Б.1, Б.2)</t>
   </si>
@@ -195,13 +195,19 @@
     <t>3. Число водопотребителей U и приборов N</t>
   </si>
   <si>
+    <t>Задано в задании</t>
+  </si>
+  <si>
     <t>U по типам квартир = Σ(N_кв.жит · n_кв) · n_эт · n_сек, чел.</t>
   </si>
   <si>
     <t>U по заселённости = заселённость · n_кв · n_эт · n_сек, чел.</t>
   </si>
   <si>
-    <t>U, принятое в расчёте (по заселённости — округление вверх), чел.</t>
+    <t>U, принятое в расчёте (задано; иначе по заселённости — округление вверх), чел.</t>
+  </si>
+  <si>
+    <t>← если U, N, N_h даны в задании готовыми числами — вписать сюда (разделы 1–2 тогда не нужны); N_h пусто — принимается равным N</t>
   </si>
   <si>
     <t>N — приборов с холодной водой (ХВС) = Σ(n_пр · n_кв) · n_эт · n_сек, шт.</t>
@@ -1320,7 +1326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B17" s="5" t="s">
         <v>25</v>
       </c>
@@ -1345,7 +1351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B18" s="11" t="s">
         <v>26</v>
       </c>
@@ -1366,81 +1372,104 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:10" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:19" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="21" spans="2:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="D20" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C21" s="14">
         <f>H18*C5*C6</f>
         <v>336</v>
       </c>
     </row>
-    <row r="22" spans="2:10" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:19" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C22" s="14">
         <f>IF(C7="","",C7*C18*C5*C6)</f>
         <v>326.39999999999998</v>
       </c>
     </row>
-    <row r="23" spans="2:10" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:19" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B23" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C23" s="15">
-        <f>IF(C7="",C21,ROUNDUP(C22,0))</f>
+        <f>IF(D23&lt;&gt;"",D23,IF(C7="",C21,ROUNDUP(C22,0)))</f>
         <v>327</v>
       </c>
-    </row>
-    <row r="24" spans="2:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="D23" s="7"/>
+      <c r="E23" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="32"/>
+      <c r="Q23" s="32"/>
+      <c r="R23" s="32"/>
+      <c r="S23" s="32"/>
+    </row>
+    <row r="24" spans="2:19" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B24" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C24" s="15">
-        <f>I18*C5*C6</f>
+        <f>IF(D24&lt;&gt;"",D24,I18*C5*C6)</f>
         <v>384</v>
       </c>
-    </row>
-    <row r="25" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B25" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C25" s="15">
-        <f>J18*C5*C6</f>
+        <f>IF(D25&lt;&gt;"",D25,IF(D24&lt;&gt;"",D24,J18*C5*C6))</f>
         <v>288</v>
       </c>
-    </row>
-    <row r="27" spans="2:10" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="D25" s="7"/>
+    </row>
+    <row r="27" spans="2:19" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" ht="31.2" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B28" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C29" s="16">
         <f>INDEX(A2_B,MATCH($C$8,A2_IMYA,0))</f>
@@ -1455,12 +1484,12 @@
         <v>110</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C30" s="16">
         <f>INDEX(A2_D,MATCH($C$8,A2_IMYA,0))</f>
@@ -1475,12 +1504,12 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C31" s="16">
         <f>INDEX(A2_F,MATCH($C$8,A2_IMYA,0))</f>
@@ -1495,12 +1524,12 @@
         <v>0.2</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C32" s="16">
         <f>INDEX(A2_H,MATCH($C$8,A2_IMYA,0))</f>
@@ -1515,12 +1544,12 @@
         <v>200</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B33" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C33" s="16">
         <f>INDEX(A2_J,MATCH($C$8,A2_IMYA,0))</f>
@@ -1535,12 +1564,12 @@
         <v>24</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B34" s="31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
@@ -1562,66 +1591,66 @@
     </row>
     <row r="36" spans="2:19" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="2:19" ht="46.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="6"/>
       <c r="C37" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="S37" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B38" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C38" s="18">
         <f>C33</f>
@@ -1694,7 +1723,7 @@
     </row>
     <row r="39" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B39" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C39" s="18">
         <f>D33</f>
@@ -1767,7 +1796,7 @@
     </row>
     <row r="40" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B40" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C40" s="18">
         <f>E33</f>
@@ -1840,7 +1869,7 @@
     </row>
     <row r="41" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B41" s="31" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C41" s="32"/>
       <c r="D41" s="32"/>
@@ -1862,41 +1891,41 @@
     </row>
     <row r="43" spans="2:19" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="2:19" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B44" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B45" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C45" s="17" t="str">
         <f>α!AB2</f>
@@ -1942,7 +1971,7 @@
     </row>
     <row r="46" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B46" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C46" s="17" t="str">
         <f>α!AB3</f>
@@ -1988,7 +2017,7 @@
     </row>
     <row r="47" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B47" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C47" s="17" t="str">
         <f>α!AB4</f>
@@ -2034,7 +2063,7 @@
     </row>
     <row r="48" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B48" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C48" s="17" t="str">
         <f>α!AB5</f>
@@ -2080,7 +2109,7 @@
     </row>
     <row r="49" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B49" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C49" s="17" t="str">
         <f>α!AB6</f>
@@ -2126,7 +2155,7 @@
     </row>
     <row r="50" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B50" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C50" s="17" t="str">
         <f>α!AB7</f>
@@ -2172,12 +2201,12 @@
     </row>
     <row r="52" spans="2:19" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="2:19" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="38" t="str">
-        <f>IF($C$7="","U = Σ(N_кв.жит·n_кв)·n_эт·n_сек = "&amp;FIXED(H18,1,TRUE)&amp;"·"&amp;C5&amp;"·"&amp;C6&amp;" = "&amp;FIXED(C23,0,TRUE)&amp;" чел.","U = заселённость·n_кв·n_эт·n_сек = "&amp;FIXED(C7,2,TRUE)&amp;"·"&amp;C18&amp;"·"&amp;C5&amp;"·"&amp;C6&amp;" = "&amp;FIXED(C22,2,TRUE)&amp;" ≈ "&amp;C23&amp;" чел.")</f>
+        <f>IF($D$23&lt;&gt;"","U = "&amp;C23&amp;" чел. (задано)",IF($C$7="","U = Σ(N_кв.жит·n_кв)·n_эт·n_сек = "&amp;FIXED(H18,1,TRUE)&amp;"·"&amp;C5&amp;"·"&amp;C6&amp;" = "&amp;FIXED(C23,0,TRUE)&amp;" чел.","U = заселённость·n_кв·n_эт·n_сек = "&amp;FIXED(C7,2,TRUE)&amp;"·"&amp;C18&amp;"·"&amp;C5&amp;"·"&amp;C6&amp;" = "&amp;FIXED(C22,2,TRUE)&amp;" ≈ "&amp;C23&amp;" чел."))</f>
         <v>U = заселённость·n_кв·n_эт·n_сек = 3,40·8·12·1 = 326,40 ≈ 327 чел.</v>
       </c>
       <c r="C53" s="32"/>
@@ -2200,7 +2229,7 @@
     </row>
     <row r="54" spans="2:19" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="38" t="str">
-        <f>"N = Σ(n_пр·n_кв)·n_эт·n_сек = "&amp;I18&amp;"·"&amp;C5&amp;"·"&amp;C6&amp;" = "&amp;C24&amp;" шт.;   N_h = "&amp;J18&amp;"·"&amp;C5&amp;"·"&amp;C6&amp;" = "&amp;C25&amp;" шт."</f>
+        <f>IF($D$24&lt;&gt;"","N = "&amp;C24&amp;" шт. (задано);   N_h = "&amp;C25&amp;" шт."&amp;IF($D$25="",IF(C25=C24," (принято равным N)","")," (задано)"),"N = Σ(n_пр·n_кв)·n_эт·n_сек = "&amp;I18&amp;"·"&amp;C5&amp;"·"&amp;C6&amp;" = "&amp;C24&amp;" шт.;   N_h = "&amp;J18&amp;"·"&amp;C5&amp;"·"&amp;C6&amp;" = "&amp;C25&amp;" шт.")</f>
         <v>N = Σ(n_пр·n_кв)·n_эт·n_сек = 32·12·1 = 384 шт.;   N_h = 24·12·1 = 288 шт.</v>
       </c>
       <c r="C54" s="32"/>
@@ -2407,7 +2436,7 @@
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B64" s="31" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C64" s="32"/>
       <c r="D64" s="32"/>
@@ -2428,7 +2457,7 @@
       <c r="S64" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
     <mergeCell ref="B64:S64"/>
     <mergeCell ref="B55:S55"/>
     <mergeCell ref="B41:S41"/>
@@ -2448,6 +2477,7 @@
     <mergeCell ref="B34:S34"/>
     <mergeCell ref="J48:S48"/>
     <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E23:S23"/>
     <mergeCell ref="B2:S2"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="J47:S47"/>
@@ -2479,96 +2509,96 @@
   <sheetData>
     <row r="1" spans="1:29" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H1" s="24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I1" s="24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K1" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L1" s="24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M1" s="24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="N1" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O1" s="24" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="P1" s="24" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q1" s="24" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="R1" s="24" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S1" s="24" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T1" s="24" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="U1" s="24" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="V1" s="24" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="W1" s="24" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="X1" s="24" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Y1" s="24" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Z1" s="24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AA1" s="24" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AB1" s="24" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AC1" s="24" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B2" s="25">
         <f>Расчёт!E38</f>
@@ -2685,7 +2715,7 @@
     </row>
     <row r="3" spans="1:29" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B3" s="25">
         <f>Расчёт!E39</f>
@@ -2802,7 +2832,7 @@
     </row>
     <row r="4" spans="1:29" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B4" s="25">
         <f>Расчёт!E40</f>
@@ -2919,7 +2949,7 @@
     </row>
     <row r="5" spans="1:29" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B5" s="25">
         <f>Расчёт!E38</f>
@@ -3036,7 +3066,7 @@
     </row>
     <row r="6" spans="1:29" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B6" s="25">
         <f>Расчёт!E39</f>
@@ -3153,7 +3183,7 @@
     </row>
     <row r="7" spans="1:29" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="25" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B7" s="25">
         <f>Расчёт!E40</f>
@@ -3270,7 +3300,7 @@
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A10" s="26" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -3285,15 +3315,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -7956,12 +7986,12 @@
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B2" s="24">
         <v>0.1</v>
@@ -9830,44 +9860,44 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I2" s="28" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B3" s="29">
         <v>70</v>
@@ -9899,7 +9929,7 @@
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B4" s="29">
         <v>110</v>
@@ -9931,7 +9961,7 @@
     </row>
     <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="29" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B5" s="29">
         <v>120</v>
@@ -9963,7 +9993,7 @@
     </row>
     <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="29" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B6" s="29">
         <v>130</v>
@@ -9995,7 +10025,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="29" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B7" s="29">
         <v>160</v>
@@ -10059,7 +10089,7 @@
     </row>
     <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="30" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="30"/>
@@ -10073,7 +10103,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="26" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
